--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -1,49 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\soft\cv_vibrometry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\soft\Personal\cv_vibrometry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DB003B-75A9-4EB2-A2F1-9471524510EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F72B79-D16E-45F0-8EB4-2EB7C196F1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C33BA12C-13D2-45F4-B160-36382B4637A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Atividades Pedagogicas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="93">
   <si>
     <t>Descrição da Tarefa</t>
   </si>
   <si>
+    <t>Início</t>
+  </si>
+  <si>
+    <t>Término</t>
+  </si>
+  <si>
+    <t>Semanas (CW)</t>
+  </si>
+  <si>
     <t>CW 27</t>
   </si>
   <si>
@@ -110,84 +101,78 @@
     <t>CW 48</t>
   </si>
   <si>
-    <t>CW 49</t>
-  </si>
-  <si>
-    <t>Início</t>
-  </si>
-  <si>
-    <t>Término</t>
-  </si>
-  <si>
     <t>Fase 1 – Desenvolvimento do Algoritmo e MVP</t>
   </si>
   <si>
+    <t>CW 27–35</t>
+  </si>
+  <si>
     <t>Implementação dos filtros de Gabor e pipeline de processamento</t>
   </si>
   <si>
+    <t>CW 27–29</t>
+  </si>
+  <si>
     <t>Construção do MVP (DJI Osmo Action 4 + régua)</t>
   </si>
   <si>
+    <t>CW 28–30</t>
+  </si>
+  <si>
     <t>Simulação da viga engastada e aquisição preliminar</t>
   </si>
   <si>
+    <t>CW 30–31</t>
+  </si>
+  <si>
     <t>Calibração inicial e validação do algoritmo</t>
   </si>
   <si>
-    <t>Marco A – MVP e algoritmo validados</t>
-  </si>
-  <si>
-    <t>Semanas (CW)</t>
-  </si>
-  <si>
-    <t>CW 27–33</t>
-  </si>
-  <si>
-    <t>CW 27–29</t>
-  </si>
-  <si>
-    <t>CW 28–30</t>
-  </si>
-  <si>
-    <t>CW 30–31</t>
-  </si>
-  <si>
-    <t>CW 32–33</t>
+    <t>CW 32–35</t>
+  </si>
+  <si>
+    <t>Marco A – MVP e algoritmo validados (TDE A)</t>
   </si>
   <si>
     <t>Fase 2 – Validação Experimental</t>
   </si>
   <si>
-    <t>CW 34–40</t>
+    <t>CW 36–40</t>
   </si>
   <si>
     <t>Setup experimental (iluminação, calibração e câmeras)</t>
   </si>
   <si>
-    <t>CW 34–36</t>
+    <t>CW 36–37</t>
   </si>
   <si>
     <t>Ensaios dinâmicos e aquisição experimental</t>
   </si>
   <si>
-    <t>CW 37–39</t>
-  </si>
-  <si>
-    <t>Marco B – Base experimental concluída</t>
+    <t>CW 38–39</t>
+  </si>
+  <si>
+    <t>Marco B – Base experimental concluída (TDE B)</t>
   </si>
   <si>
     <t>Fase 3 – Processamento e Análise</t>
   </si>
   <si>
+    <t>CW 32–43</t>
+  </si>
+  <si>
+    <t>Processamento digital e filtragem dos sinais</t>
+  </si>
+  <si>
+    <t>CW 32–41</t>
+  </si>
+  <si>
     <t>Extração de deslocamentos sub-pixel</t>
   </si>
   <si>
     <t>CW 41–42</t>
   </si>
   <si>
-    <t>Processamento digital e filtragem dos sinais</t>
-  </si>
-  <si>
     <t>Avaliação de SHM e interpretação dos resultados</t>
   </si>
   <si>
@@ -197,32 +182,131 @@
     <t>Fase 4 – Escrita e Finalização</t>
   </si>
   <si>
+    <t>CW 30–44</t>
+  </si>
+  <si>
+    <t>Escrita da metodologia, resultados e discussão</t>
+  </si>
+  <si>
+    <t>Revisão com orientador e ajustes finais</t>
+  </si>
+  <si>
     <t>CW 43–44</t>
   </si>
   <si>
-    <t>Marco D – Submissão do TCC</t>
-  </si>
-  <si>
-    <t>Escrita da metodologia, resultados e discussão</t>
-  </si>
-  <si>
-    <t>Revisão com orientador e ajustes finais</t>
-  </si>
-  <si>
-    <t>CW 32–43</t>
-  </si>
-  <si>
-    <t>CW 32–41</t>
-  </si>
-  <si>
-    <t>CW 30–44</t>
+    <t>Marco D – Submissão do TCC (TDE C/D)</t>
+  </si>
+  <si>
+    <t>Fase 5 – Defesa e Revisão Final</t>
+  </si>
+  <si>
+    <t>CW 45–48</t>
+  </si>
+  <si>
+    <t>Preparação para a banca de defesa</t>
+  </si>
+  <si>
+    <t>Marco E – Banca de Defesa (Encontro Defesa, 12/11)</t>
+  </si>
+  <si>
+    <t>Ajustes pós-banca e correção do artigo</t>
+  </si>
+  <si>
+    <t>CW 46–47</t>
+  </si>
+  <si>
+    <t>Marco F – Entrega do Artigo corrigido pós banca (TDE E)</t>
+  </si>
+  <si>
+    <t>5.  CRONOGRAMA DE ATIVIDADES PEDAGÓGICAS</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>Descrição das atividades pedagógicas</t>
+  </si>
+  <si>
+    <t>Carga horária</t>
+  </si>
+  <si>
+    <t>TDE (Integração)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Semana de Integração Acadêmica</t>
+  </si>
+  <si>
+    <t>1ha</t>
+  </si>
+  <si>
+    <t>Encontro iniciais</t>
+  </si>
+  <si>
+    <t>RA1</t>
+  </si>
+  <si>
+    <t>Acolhida; Metodologia; Orientação dos TDEs</t>
+  </si>
+  <si>
+    <t>TDE (A)</t>
+  </si>
+  <si>
+    <t>TDE (A): Ajustes do cronograma (até 30/08/2026)</t>
+  </si>
+  <si>
+    <t>2ha</t>
+  </si>
+  <si>
+    <t>TDE (B)</t>
+  </si>
+  <si>
+    <t>TDE (B): Entrega do Artigo (parcial) (até 03/10/2026)</t>
+  </si>
+  <si>
+    <t>6ha</t>
+  </si>
+  <si>
+    <t>TDE (C)</t>
+  </si>
+  <si>
+    <t>TDE (C): Entrega Documental do Artigo (até 01/11/2026)</t>
+  </si>
+  <si>
+    <t>8ha</t>
+  </si>
+  <si>
+    <t>TDE (D)</t>
+  </si>
+  <si>
+    <t>TDE (D): Entrega Vídeo (até 01/11/2026)</t>
+  </si>
+  <si>
+    <t>Encontro Defesa</t>
+  </si>
+  <si>
+    <t>Bancas de defesa (12/11/2026)</t>
+  </si>
+  <si>
+    <t>TDE (E)</t>
+  </si>
+  <si>
+    <t>TDE (E): Entrega Documental do Artigo corrigido pós banca (até 23/11/2026)</t>
+  </si>
+  <si>
+    <t>TOTAL: 20ha = 15h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +327,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF7030A0"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,8 +401,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DC3E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -323,11 +435,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -369,17 +520,35 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFFF469"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -707,100 +876,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94F2732-AD43-454E-A204-B23134912FF4}">
-  <dimension ref="A1:AA20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
-    <col min="2" max="3" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
-    <col min="23" max="27" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -808,10 +979,10 @@
         <v>46202</v>
       </c>
       <c r="C2" s="6">
-        <v>46250</v>
+        <v>46264</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -820,8 +991,8 @@
       <c r="I2" s="8"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -835,11 +1006,10 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-    </row>
-    <row r="3" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2">
         <v>46202</v>
@@ -848,7 +1018,7 @@
         <v>46222</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
@@ -872,11 +1042,10 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-    </row>
-    <row r="4" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>46209</v>
@@ -885,7 +1054,7 @@
         <v>46229</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="10"/>
@@ -909,11 +1078,10 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-    </row>
-    <row r="5" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2">
         <v>46223</v>
@@ -922,7 +1090,7 @@
         <v>46236</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -946,20 +1114,19 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-    </row>
-    <row r="6" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2">
         <v>46237</v>
       </c>
       <c r="C6" s="2">
-        <v>46250</v>
+        <v>46264</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -968,8 +1135,8 @@
       <c r="I6" s="3"/>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -983,20 +1150,19 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-    </row>
-    <row r="7" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="C7" s="2">
-        <v>46250</v>
+        <v>46264</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1004,9 +1170,9 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="5"/>
+      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="M7" s="5"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1020,20 +1186,19 @@
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-    </row>
-    <row r="8" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46265</v>
+      </c>
+      <c r="C8" s="6">
+        <v>46298</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B8" s="6">
-        <v>46251</v>
-      </c>
-      <c r="C8" s="6">
-        <v>46299</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1042,8 +1207,8 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
@@ -1057,20 +1222,19 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-    </row>
-    <row r="9" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B9" s="2">
-        <v>46251</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46271</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1079,10 +1243,10 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
       <c r="N9" s="10"/>
-      <c r="O9" s="3"/>
+      <c r="O9" s="10"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -1094,20 +1258,19 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-    </row>
-    <row r="10" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="C10" s="2">
         <v>46292</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1119,7 +1282,7 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="11"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
       <c r="R10" s="3"/>
@@ -1131,20 +1294,19 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-    </row>
-    <row r="11" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2">
         <v>46293</v>
       </c>
       <c r="C11" s="2">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1168,11 +1330,10 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="6">
         <v>46237</v>
@@ -1181,35 +1342,34 @@
         <v>46320</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-    </row>
-    <row r="13" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2">
         <v>46237</v>
@@ -1218,7 +1378,7 @@
         <v>46306</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1242,11 +1402,10 @@
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-    </row>
-    <row r="14" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
         <v>46300</v>
@@ -1255,7 +1414,7 @@
         <v>46313</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1279,11 +1438,10 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-    </row>
-    <row r="15" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2">
         <v>46314</v>
@@ -1292,7 +1450,7 @@
         <v>46320</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1316,11 +1474,10 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-    </row>
-    <row r="16" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2">
         <v>46314</v>
@@ -1329,7 +1486,7 @@
         <v>46320</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1353,11 +1510,10 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="6">
         <v>46223</v>
@@ -1366,7 +1522,7 @@
         <v>46327</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1390,9 +1546,8 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-    </row>
-    <row r="18" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>54</v>
       </c>
@@ -1403,7 +1558,7 @@
         <v>46327</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1427,9 +1582,8 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-    </row>
-    <row r="19" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>55</v>
       </c>
@@ -1440,7 +1594,7 @@
         <v>46327</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1464,11 +1618,10 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2">
         <v>46321</v>
@@ -1477,7 +1630,7 @@
         <v>46327</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1501,9 +1654,356 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
-      <c r="AA20" s="3"/>
+    </row>
+    <row r="21" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="6">
+        <v>46328</v>
+      </c>
+      <c r="C21" s="6">
+        <v>46349</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="7"/>
+    </row>
+    <row r="22" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46328</v>
+      </c>
+      <c r="C22" s="2">
+        <v>46334</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+    </row>
+    <row r="23" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46338</v>
+      </c>
+      <c r="C23" s="2">
+        <v>46338</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+    </row>
+    <row r="24" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46339</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46348</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="3"/>
+    </row>
+    <row r="25" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46349</v>
+      </c>
+      <c r="C25" s="2">
+        <v>46349</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{19540963-e559-4020-8a90-fe8a502c2801}" enabled="1" method="Standard" siteId="{f25493ae-1c98-41d7-8a33-0be75f5fe603}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>